--- a/pregenerated_results/ate_iptw_cox_time_interaction_IPTW_Cox_TimeInteraction_retention.xlsx
+++ b/pregenerated_results/ate_iptw_cox_time_interaction_IPTW_Cox_TimeInteraction_retention.xlsx
@@ -609,7 +609,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>gender_Male</t>
+          <t>job_family_Market_Access</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -618,13 +618,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.024</v>
+        <v>0.005</v>
       </c>
       <c r="D7" t="n">
-        <v>0.027</v>
+        <v>-0.013</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.002999999999999999</v>
+        <v>-0.008</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -636,7 +636,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>gender_Non_Binary_Other</t>
+          <t>job_family_Pharmacovigilance</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -645,13 +645,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.046</v>
+        <v>-0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.002</v>
+        <v>-0.004</v>
       </c>
       <c r="E8" t="n">
-        <v>0.044</v>
+        <v>-0.004</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -663,7 +663,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_family_Communications</t>
+          <t>performance_rating_Meets</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -672,16 +672,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.401</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.001</v>
+        <v>-0.038</v>
       </c>
       <c r="E9" t="n">
-        <v>0.008</v>
+        <v>0.363</v>
       </c>
       <c r="F9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -690,7 +690,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>job_family_Data_Science</t>
+          <t>organization_Digital</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -699,16 +699,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.074</v>
+        <v>0.197</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.042</v>
+        <v>0.065</v>
       </c>
       <c r="E10" t="n">
-        <v>0.03199999999999999</v>
+        <v>0.132</v>
       </c>
       <c r="F10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -717,7 +717,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_family_Finance_and_Accounting</t>
+          <t>job_family_Communications</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -726,13 +726,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.034</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.008</v>
+        <v>-0.001</v>
       </c>
       <c r="E11" t="n">
-        <v>0.026</v>
+        <v>0.008</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -744,7 +744,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>job_family_Human_Resources</t>
+          <t>job_family_Finance_and_Accounting</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.023</v>
+        <v>0.034</v>
       </c>
       <c r="D12" t="n">
-        <v>0.01</v>
+        <v>-0.008</v>
       </c>
       <c r="E12" t="n">
-        <v>0.013</v>
+        <v>0.026</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -771,7 +771,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>job_family_IT_and_Digital</t>
+          <t>job_family_Human_Resources</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -780,13 +780,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.007</v>
+        <v>0.023</v>
       </c>
       <c r="D13" t="n">
-        <v>0.025</v>
+        <v>0.01</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.018</v>
+        <v>0.013</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -798,7 +798,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>job_family_Legal_and_Compliance</t>
+          <t>job_family_Data_Science</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.041</v>
+        <v>-0.074</v>
       </c>
       <c r="D14" t="n">
-        <v>0.038</v>
+        <v>-0.042</v>
       </c>
       <c r="E14" t="n">
-        <v>0.003000000000000003</v>
+        <v>0.03199999999999999</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -825,7 +825,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_family_Market_Access</t>
+          <t>region_Europe</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -834,16 +834,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.005</v>
+        <v>0.107</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.013</v>
+        <v>0.042</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.008</v>
+        <v>0.065</v>
       </c>
       <c r="F15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
@@ -852,7 +852,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_family_Marketing</t>
+          <t>job_family_Sales</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.032</v>
+        <v>-0.019</v>
       </c>
       <c r="D16" t="n">
-        <v>0.03</v>
+        <v>-0.023</v>
       </c>
       <c r="E16" t="n">
-        <v>0.002000000000000002</v>
+        <v>-0.004</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -879,7 +879,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>job_family_Medical_Affairs</t>
+          <t>job_family_Marketing</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -888,13 +888,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.014</v>
+        <v>0.032</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.003</v>
+        <v>0.03</v>
       </c>
       <c r="E17" t="n">
-        <v>0.011</v>
+        <v>0.002000000000000002</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -906,7 +906,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_family_Pharmacovigilance</t>
+          <t>organization_RandD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -915,16 +915,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0</v>
+        <v>0.227</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.004</v>
+        <v>0.022</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.004</v>
+        <v>0.205</v>
       </c>
       <c r="F18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
@@ -933,7 +933,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_family_Quality_Assurance</t>
+          <t>performance_rating_Far_Exceeds</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -942,16 +942,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.008</v>
+        <v>0.392</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.001</v>
+        <v>0.03</v>
       </c>
       <c r="E19" t="n">
-        <v>0.007</v>
+        <v>0.362</v>
       </c>
       <c r="F19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -960,7 +960,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>job_family_Regulatory_Affairs</t>
+          <t>region_Latin_America</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -969,13 +969,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.077</v>
+        <v>-0.041</v>
       </c>
       <c r="D20" t="n">
-        <v>0.031</v>
+        <v>-0.013</v>
       </c>
       <c r="E20" t="n">
-        <v>0.046</v>
+        <v>0.028</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -987,7 +987,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_family_Sales</t>
+          <t>job_family_Regulatory_Affairs</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.019</v>
+        <v>0.077</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.023</v>
+        <v>0.031</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.004</v>
+        <v>0.046</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -1014,7 +1014,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>job_family_Supply_Chain</t>
+          <t>job_family_Legal_and_Compliance</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1023,16 +1023,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.113</v>
+        <v>0.041</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.05</v>
+        <v>0.038</v>
       </c>
       <c r="E22" t="n">
-        <v>0.063</v>
+        <v>0.003000000000000003</v>
       </c>
       <c r="F22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
@@ -1041,7 +1041,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>organization_Digital</t>
+          <t>region_Middle_East_and_Africa</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1050,16 +1050,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.197</v>
+        <v>-0.066</v>
       </c>
       <c r="D23" t="n">
-        <v>0.065</v>
+        <v>-0.057</v>
       </c>
       <c r="E23" t="n">
-        <v>0.132</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="F23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="b">
         <v>1</v>
@@ -1068,7 +1068,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>organization_Finance</t>
+          <t>job_family_Medical_Affairs</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1077,16 +1077,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.143</v>
+        <v>-0.014</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.042</v>
+        <v>-0.003</v>
       </c>
       <c r="E24" t="n">
-        <v>0.101</v>
+        <v>0.011</v>
       </c>
       <c r="F24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
@@ -1095,7 +1095,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>organization_HR</t>
+          <t>job_family_IT_and_Digital</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1104,13 +1104,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-0.054</v>
+        <v>0.007</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.027</v>
+        <v>0.025</v>
       </c>
       <c r="E25" t="n">
-        <v>0.027</v>
+        <v>-0.018</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -1122,7 +1122,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>organization_Manufacturing</t>
+          <t>region_North_America</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1131,16 +1131,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-0.128</v>
+        <v>0.022</v>
       </c>
       <c r="D26" t="n">
-        <v>0.019</v>
+        <v>0.015</v>
       </c>
       <c r="E26" t="n">
-        <v>0.109</v>
+        <v>0.006999999999999999</v>
       </c>
       <c r="F26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="b">
         <v>1</v>
@@ -1149,7 +1149,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>organization_RandD</t>
+          <t>job_family_Supply_Chain</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1158,13 +1158,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.227</v>
+        <v>-0.113</v>
       </c>
       <c r="D27" t="n">
-        <v>0.022</v>
+        <v>-0.05</v>
       </c>
       <c r="E27" t="n">
-        <v>0.205</v>
+        <v>0.063</v>
       </c>
       <c r="F27" t="b">
         <v>0</v>
@@ -1176,7 +1176,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>performance_rating_Far_Exceeds</t>
+          <t>gender_Male</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1185,16 +1185,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.392</v>
+        <v>-0.024</v>
       </c>
       <c r="D28" t="n">
-        <v>0.03</v>
+        <v>0.027</v>
       </c>
       <c r="E28" t="n">
-        <v>0.362</v>
+        <v>-0.002999999999999999</v>
       </c>
       <c r="F28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="b">
         <v>1</v>
@@ -1203,7 +1203,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>performance_rating_Meets</t>
+          <t>job_family_Quality_Assurance</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1212,16 +1212,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-0.401</v>
+        <v>-0.008</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.038</v>
+        <v>-0.001</v>
       </c>
       <c r="E29" t="n">
-        <v>0.363</v>
+        <v>0.007</v>
       </c>
       <c r="F29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" t="b">
         <v>1</v>
@@ -1230,7 +1230,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>region_Europe</t>
+          <t>organization_Manufacturing</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1239,13 +1239,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.107</v>
+        <v>-0.128</v>
       </c>
       <c r="D30" t="n">
-        <v>0.042</v>
+        <v>0.019</v>
       </c>
       <c r="E30" t="n">
-        <v>0.065</v>
+        <v>0.109</v>
       </c>
       <c r="F30" t="b">
         <v>0</v>
@@ -1257,7 +1257,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>region_Latin_America</t>
+          <t>organization_Finance</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1266,16 +1266,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-0.041</v>
+        <v>-0.143</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.013</v>
+        <v>-0.042</v>
       </c>
       <c r="E31" t="n">
-        <v>0.028</v>
+        <v>0.101</v>
       </c>
       <c r="F31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="b">
         <v>1</v>
@@ -1284,7 +1284,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>region_Middle_East_and_Africa</t>
+          <t>organization_HR</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1293,13 +1293,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-0.066</v>
+        <v>-0.054</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.057</v>
+        <v>-0.027</v>
       </c>
       <c r="E32" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.027</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -1311,7 +1311,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>region_North_America</t>
+          <t>gender_Non_Binary_Other</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1320,13 +1320,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.022</v>
+        <v>0.046</v>
       </c>
       <c r="D33" t="n">
-        <v>0.015</v>
+        <v>-0.002</v>
       </c>
       <c r="E33" t="n">
-        <v>0.006999999999999999</v>
+        <v>0.044</v>
       </c>
       <c r="F33" t="b">
         <v>1</v>
@@ -1400,13 +1400,13 @@
         <v>0.1325095691671194</v>
       </c>
       <c r="E2" t="n">
-        <v>1.678870188120527</v>
+        <v>1.678870188120528</v>
       </c>
       <c r="F2" t="n">
         <v>1.124267686541995</v>
       </c>
       <c r="G2" t="n">
-        <v>1.678043421071839</v>
+        <v>1.67804342107184</v>
       </c>
     </row>
   </sheetData>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>reference period</t>
+          <t>reference period (timepoint_days = period end)</t>
         </is>
       </c>
     </row>
@@ -1709,13 +1709,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-2.680600179802939</v>
+        <v>-2.680600179802941</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4771933030981503</v>
+        <v>0.477193303098152</v>
       </c>
       <c r="D2" t="n">
-        <v>1.938181768273511e-08</v>
+        <v>1.938181768273688e-08</v>
       </c>
     </row>
     <row r="3">
@@ -1725,13 +1725,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.02542074333516161</v>
+        <v>-0.02542074333516158</v>
       </c>
       <c r="C3" t="n">
         <v>0.1002143663033998</v>
       </c>
       <c r="D3" t="n">
-        <v>0.79975540801217</v>
+        <v>0.7997554080121703</v>
       </c>
     </row>
     <row r="4">
@@ -1741,10 +1741,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2244463748843409</v>
+        <v>0.2244463748843408</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2335027157442915</v>
+        <v>0.2335027157442914</v>
       </c>
       <c r="D4" t="n">
         <v>0.3364439424069162</v>
@@ -1757,13 +1757,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8155080917228588</v>
+        <v>0.8155080917228589</v>
       </c>
       <c r="C5" t="n">
         <v>0.173402651392118</v>
       </c>
       <c r="D5" t="n">
-        <v>2.563995828054386e-06</v>
+        <v>2.563995828054396e-06</v>
       </c>
     </row>
     <row r="6">
@@ -1773,13 +1773,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03527526670387308</v>
+        <v>0.03527526670387304</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1916882946919544</v>
+        <v>0.1916882946919543</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8539945454713548</v>
+        <v>0.8539945454713549</v>
       </c>
     </row>
     <row r="7">
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2773648159307716</v>
+        <v>0.2773648159307717</v>
       </c>
       <c r="C7" t="n">
         <v>0.1901447102133385</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1446466431125523</v>
+        <v>0.1446466431125524</v>
       </c>
     </row>
     <row r="8">
@@ -1805,13 +1805,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1036811851537241</v>
+        <v>0.1036811851537242</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1952515666982444</v>
+        <v>0.1952515666982446</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5954095400432469</v>
+        <v>0.5954095400432466</v>
       </c>
     </row>
     <row r="9">
@@ -1821,13 +1821,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8738774480300985</v>
+        <v>0.8738774480300986</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1695280942409139</v>
+        <v>0.1695280942409138</v>
       </c>
       <c r="D9" t="n">
-        <v>2.539495077342821e-07</v>
+        <v>2.539495077342793e-07</v>
       </c>
     </row>
     <row r="10">
@@ -1837,13 +1837,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.0445652077261707</v>
+        <v>-0.04456520772617081</v>
       </c>
       <c r="C10" t="n">
-        <v>0.260402103171632</v>
+        <v>0.2604021031716311</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8641137091517843</v>
+        <v>0.8641137091517835</v>
       </c>
     </row>
     <row r="11">
@@ -1853,13 +1853,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.2737623724798146</v>
+        <v>-0.2737623724798149</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2787881385465067</v>
+        <v>0.2787881385465062</v>
       </c>
       <c r="D11" t="n">
-        <v>0.326113242387764</v>
+        <v>0.3261132423877625</v>
       </c>
     </row>
     <row r="12">
@@ -1869,13 +1869,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.08100487957118148</v>
+        <v>0.08100487957118127</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2596429772097172</v>
+        <v>0.2596429772097175</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7550514391424692</v>
+        <v>0.75505143914247</v>
       </c>
     </row>
     <row r="13">
@@ -1885,13 +1885,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03917827337461754</v>
+        <v>0.03917827337461743</v>
       </c>
       <c r="C13" t="n">
         <v>0.2572958805743774</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8789745077123743</v>
+        <v>0.8789745077123745</v>
       </c>
     </row>
     <row r="14">
@@ -1901,10 +1901,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.05296103812307935</v>
+        <v>-0.05296103812307931</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2610089865588724</v>
+        <v>0.2610089865588721</v>
       </c>
       <c r="D14" t="n">
         <v>0.8392062624375534</v>
@@ -1917,10 +1917,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1181322726534161</v>
+        <v>0.1181322726534159</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2572294350577187</v>
+        <v>0.2572294350577182</v>
       </c>
       <c r="D15" t="n">
         <v>0.6460556128984086</v>
@@ -1933,13 +1933,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.004000986240379481</v>
+        <v>-0.004000986240379549</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2383903410311192</v>
+        <v>0.2383903410311187</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9866094604655132</v>
+        <v>0.986609460465513</v>
       </c>
     </row>
     <row r="17">
@@ -1949,13 +1949,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1057185310395306</v>
+        <v>0.1057185310395303</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2543340222421759</v>
+        <v>0.2543340222421755</v>
       </c>
       <c r="D17" t="n">
-        <v>0.677652912256731</v>
+        <v>0.6776529122567312</v>
       </c>
     </row>
     <row r="18">
@@ -1965,13 +1965,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1377694895733254</v>
+        <v>-0.1377694895733256</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2636874203313636</v>
+        <v>0.263687420331363</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6013412201546282</v>
+        <v>0.6013412201546265</v>
       </c>
     </row>
     <row r="19">
@@ -1981,13 +1981,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.02557154094223237</v>
+        <v>-0.02557154094223246</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2527597901538116</v>
+        <v>0.2527597901538113</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9194160355966677</v>
+        <v>0.9194160355966674</v>
       </c>
     </row>
     <row r="20">
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.07344622569376411</v>
+        <v>-0.07344622569376417</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2674578609541021</v>
+        <v>0.2674578609541011</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7836169672222787</v>
+        <v>0.7836169672222777</v>
       </c>
     </row>
     <row r="21">
@@ -2013,13 +2013,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2063167170305062</v>
+        <v>0.206316717030506</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2442896532450728</v>
+        <v>0.2442896532450723</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3983578134719854</v>
+        <v>0.3983578134719851</v>
       </c>
     </row>
     <row r="22">
@@ -2032,10 +2032,10 @@
         <v>-0.1704634573362028</v>
       </c>
       <c r="C22" t="n">
-        <v>0.269674845496591</v>
+        <v>0.26967484549659</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5273167196806365</v>
+        <v>0.527316719680635</v>
       </c>
     </row>
     <row r="23">
@@ -2045,13 +2045,13 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.5008110927334755</v>
+        <v>-0.5008110927334757</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2870672180445716</v>
+        <v>0.2870672180445714</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0810583897517186</v>
+        <v>0.08105838975171822</v>
       </c>
     </row>
     <row r="24">
@@ -2061,13 +2061,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9366864721074268</v>
+        <v>0.9366864721074269</v>
       </c>
       <c r="C24" t="n">
         <v>0.1483430409733375</v>
       </c>
       <c r="D24" t="n">
-        <v>2.713396260923871e-10</v>
+        <v>2.713396260923852e-10</v>
       </c>
     </row>
     <row r="25">
@@ -2077,13 +2077,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.5776106069409677</v>
+        <v>-0.5776106069409674</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1143619392421806</v>
+        <v>0.1143619392421807</v>
       </c>
       <c r="D25" t="n">
-        <v>4.401383208103854e-07</v>
+        <v>4.401383208104e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2093,7 +2093,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2373161448441742</v>
+        <v>0.2373161448441743</v>
       </c>
       <c r="C26" t="n">
         <v>0.1503781926377481</v>
@@ -2109,13 +2109,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.04350476117998643</v>
+        <v>-0.04350476117998649</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1611879340386415</v>
+        <v>0.1611879340386414</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7872365295400221</v>
+        <v>0.7872365295400217</v>
       </c>
     </row>
     <row r="28">
@@ -2125,13 +2125,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.07514354096975739</v>
+        <v>-0.07514354096975728</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1613683918223571</v>
+        <v>0.1613683918223568</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6414556246120158</v>
+        <v>0.6414556246120157</v>
       </c>
     </row>
     <row r="29">
@@ -2141,13 +2141,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09749293462742094</v>
+        <v>0.09749293462742106</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1543265796290169</v>
+        <v>0.1543265796290166</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5275624553510021</v>
+        <v>0.5275624553510007</v>
       </c>
     </row>
     <row r="30">
@@ -2157,13 +2157,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2280638724458788</v>
+        <v>0.2280638724458785</v>
       </c>
       <c r="C30" t="n">
         <v>0.1146565719927948</v>
       </c>
       <c r="D30" t="n">
-        <v>0.04668969945129902</v>
+        <v>0.0466896994512992</v>
       </c>
     </row>
     <row r="31">
@@ -2173,13 +2173,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.005012017390962181</v>
+        <v>-0.005012017390962146</v>
       </c>
       <c r="C31" t="n">
-        <v>0.008304876992454899</v>
+        <v>0.008304876992455041</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5461741835341518</v>
+        <v>0.5461741835341615</v>
       </c>
     </row>
     <row r="32">
@@ -2189,13 +2189,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.002418133412192865</v>
+        <v>-0.002418133412192864</v>
       </c>
       <c r="C32" t="n">
-        <v>0.007135781003458533</v>
+        <v>0.007135781003458523</v>
       </c>
       <c r="D32" t="n">
-        <v>0.7347043603418282</v>
+        <v>0.7347043603418278</v>
       </c>
     </row>
     <row r="33">
@@ -2205,13 +2205,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.004129656026475429</v>
+        <v>-0.004129656026475439</v>
       </c>
       <c r="C33" t="n">
-        <v>0.02222260881033176</v>
+        <v>0.02222260881033177</v>
       </c>
       <c r="D33" t="n">
-        <v>0.8525770672961277</v>
+        <v>0.8525770672961275</v>
       </c>
     </row>
     <row r="34">
@@ -2221,13 +2221,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.006335499136474494</v>
+        <v>0.006335499136474509</v>
       </c>
       <c r="C34" t="n">
-        <v>0.006871422968197173</v>
+        <v>0.0068714229681972</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3565249957666431</v>
+        <v>0.3565249957666438</v>
       </c>
     </row>
   </sheetData>
@@ -2281,13 +2281,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9350702643084905</v>
+        <v>0.9350702643084913</v>
       </c>
       <c r="D2" t="n">
         <v>0.8939763606698742</v>
       </c>
       <c r="E2" t="n">
-        <v>0.04109390363861631</v>
+        <v>0.04109390363861709</v>
       </c>
     </row>
     <row r="3">
@@ -2300,13 +2300,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.900193688823673</v>
+        <v>0.9001936888236747</v>
       </c>
       <c r="D3" t="n">
         <v>0.8548025202490657</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04539116857460734</v>
+        <v>0.04539116857460901</v>
       </c>
     </row>
     <row r="4">
@@ -2319,13 +2319,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.8720187983946986</v>
+        <v>0.8720187983947002</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8250397507431096</v>
+        <v>0.8250397507431066</v>
       </c>
       <c r="E4" t="n">
-        <v>0.046979047651589</v>
+        <v>0.04697904765159355</v>
       </c>
     </row>
     <row r="5">
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.8436439126637503</v>
+        <v>0.8436439126637518</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7967552731684104</v>
+        <v>0.7967552731684091</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04688863949533983</v>
+        <v>0.04688863949534272</v>
       </c>
     </row>
   </sheetData>
@@ -2385,10 +2385,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>294.5429333691336</v>
+        <v>294.5429333691335</v>
       </c>
       <c r="B2" t="n">
-        <v>5.090005783081747e-66</v>
+        <v>5.090005783082038e-66</v>
       </c>
       <c r="C2" t="n">
         <v>216.8995869671257</v>
@@ -2421,13 +2421,13 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1.142274341703322</v>
+        <v>1.142274341703325</v>
       </c>
       <c r="B5" t="n">
-        <v>0.2851722601515755</v>
+        <v>0.2851722601515749</v>
       </c>
       <c r="C5" t="n">
-        <v>1.810094443007923</v>
+        <v>1.810094443007927</v>
       </c>
       <c r="D5" t="inlineStr"/>
     </row>
@@ -2445,205 +2445,205 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1.255849807558128</v>
+        <v>1.255849807558127</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2624381298008737</v>
+        <v>0.2624381298008739</v>
       </c>
       <c r="C7" t="n">
-        <v>1.929950749633188</v>
+        <v>1.929950749633187</v>
       </c>
       <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1.566766284228123</v>
+        <v>1.566766284228121</v>
       </c>
       <c r="B8" t="n">
-        <v>0.2106772497604386</v>
+        <v>0.2106772497604389</v>
       </c>
       <c r="C8" t="n">
-        <v>2.246893563503258</v>
+        <v>2.246893563503256</v>
       </c>
       <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6.574957324834573</v>
+        <v>6.574957324834562</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0103423483000429</v>
+        <v>0.01034234830004294</v>
       </c>
       <c r="C9" t="n">
-        <v>6.595292393273068</v>
+        <v>6.595292393273063</v>
       </c>
       <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.7436106862930127</v>
+        <v>0.7436106862930084</v>
       </c>
       <c r="B10" t="n">
-        <v>0.3885066958396539</v>
+        <v>0.3885066958396552</v>
       </c>
       <c r="C10" t="n">
-        <v>1.363988631463082</v>
+        <v>1.363988631463077</v>
       </c>
       <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1.108437182271648</v>
+        <v>1.108437182271642</v>
       </c>
       <c r="B11" t="n">
-        <v>0.2924219228644682</v>
+        <v>0.2924219228644696</v>
       </c>
       <c r="C11" t="n">
-        <v>1.773876620730236</v>
+        <v>1.77387662073023</v>
       </c>
       <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.3303658657160209</v>
+        <v>0.3303658657160168</v>
       </c>
       <c r="B12" t="n">
-        <v>0.5654437324694613</v>
+        <v>0.5654437324694639</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8225446266866068</v>
+        <v>0.8225446266866003</v>
       </c>
       <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2.557369788172986</v>
+        <v>2.557369788172973</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1097810910580784</v>
+        <v>0.1097810910580795</v>
       </c>
       <c r="C13" t="n">
-        <v>3.187298512183359</v>
+        <v>3.187298512183345</v>
       </c>
       <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.9003581826524341</v>
+        <v>0.9003581826524326</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3426856873782383</v>
+        <v>0.3426856873782387</v>
       </c>
       <c r="C14" t="n">
-        <v>1.54504215742082</v>
+        <v>1.545042157420818</v>
       </c>
       <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1.432237332778618</v>
+        <v>1.432237332778611</v>
       </c>
       <c r="B15" t="n">
-        <v>0.231399651405413</v>
+        <v>0.2313996514054142</v>
       </c>
       <c r="C15" t="n">
-        <v>2.111541403804365</v>
+        <v>2.111541403804358</v>
       </c>
       <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2.063235339674781</v>
+        <v>2.063235339674773</v>
       </c>
       <c r="B16" t="n">
-        <v>0.1508895055131311</v>
+        <v>0.150889505513132</v>
       </c>
       <c r="C16" t="n">
-        <v>2.728435626137821</v>
+        <v>2.728435626137813</v>
       </c>
       <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.1958606284066906</v>
+        <v>0.1958606284066892</v>
       </c>
       <c r="B17" t="n">
-        <v>0.6580829806410341</v>
+        <v>0.6580829806410352</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6036585835541354</v>
+        <v>0.6036585835541329</v>
       </c>
       <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>5.617202257648775</v>
+        <v>5.617202257648769</v>
       </c>
       <c r="B18" t="n">
-        <v>0.01778501760915541</v>
+        <v>0.01778501760915551</v>
       </c>
       <c r="C18" t="n">
-        <v>5.813193786944902</v>
+        <v>5.813193786944894</v>
       </c>
       <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1.417029330831435</v>
+        <v>1.417029330831425</v>
       </c>
       <c r="B19" t="n">
-        <v>0.2338929801225866</v>
+        <v>0.2338929801225883</v>
       </c>
       <c r="C19" t="n">
-        <v>2.096079532445891</v>
+        <v>2.09607953244588</v>
       </c>
       <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>3.645392438578103</v>
+        <v>3.645392438578105</v>
       </c>
       <c r="B20" t="n">
-        <v>0.05622455201226811</v>
+        <v>0.05622455201226794</v>
       </c>
       <c r="C20" t="n">
-        <v>4.152655928876195</v>
+        <v>4.152655928876199</v>
       </c>
       <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.2902145522598131</v>
+        <v>0.2902145522598124</v>
       </c>
       <c r="B21" t="n">
-        <v>0.5900830729575457</v>
+        <v>0.5900830729575461</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7610100209091339</v>
+        <v>0.7610100209091329</v>
       </c>
       <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3.463998911237538</v>
+        <v>3.463998911237524</v>
       </c>
       <c r="B22" t="n">
-        <v>0.06271846142450671</v>
+        <v>0.06271846142450754</v>
       </c>
       <c r="C22" t="n">
-        <v>3.994966021304706</v>
+        <v>3.994966021304686</v>
       </c>
       <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.007612562333023125</v>
+        <v>0.007612562333023134</v>
       </c>
       <c r="B23" t="n">
-        <v>0.9304727973639381</v>
+        <v>0.930472797363938</v>
       </c>
       <c r="C23" t="n">
-        <v>0.103964121585</v>
+        <v>0.1039641215850002</v>
       </c>
       <c r="D23" t="inlineStr"/>
     </row>
@@ -2661,13 +2661,13 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.4093029449366675</v>
+        <v>0.4093029449366652</v>
       </c>
       <c r="B25" t="n">
-        <v>0.522323515132993</v>
+        <v>0.5223235151329941</v>
       </c>
       <c r="C25" t="n">
-        <v>0.936984439229875</v>
+        <v>0.9369844392298718</v>
       </c>
       <c r="D25" t="inlineStr"/>
     </row>
@@ -2685,49 +2685,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.03913855261814776</v>
+        <v>0.03913855261814755</v>
       </c>
       <c r="B27" t="n">
-        <v>0.8431744274775989</v>
+        <v>0.8431744274775992</v>
       </c>
       <c r="C27" t="n">
-        <v>0.2460969825501762</v>
+        <v>0.2460969825501756</v>
       </c>
       <c r="D27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.1260727750054029</v>
+        <v>0.1260727750054018</v>
       </c>
       <c r="B28" t="n">
-        <v>0.7225391866368589</v>
+        <v>0.7225391866368602</v>
       </c>
       <c r="C28" t="n">
-        <v>0.468852261137606</v>
+        <v>0.4688522611376033</v>
       </c>
       <c r="D28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.2420351704626638</v>
+        <v>0.242035170462663</v>
       </c>
       <c r="B29" t="n">
-        <v>0.6227400561675764</v>
+        <v>0.622740056167577</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6832980150045683</v>
+        <v>0.683298015004567</v>
       </c>
       <c r="D29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.7834052395931974</v>
+        <v>0.7834052395931964</v>
       </c>
       <c r="B30" t="n">
-        <v>0.3761017155639725</v>
+        <v>0.3761017155639729</v>
       </c>
       <c r="C30" t="n">
-        <v>1.410805207732779</v>
+        <v>1.410805207732777</v>
       </c>
       <c r="D30" t="inlineStr"/>
     </row>
@@ -2736,82 +2736,82 @@
         <v>2.446774758348333</v>
       </c>
       <c r="B31" t="n">
-        <v>0.1177666210589445</v>
+        <v>0.1177666210589444</v>
       </c>
       <c r="C31" t="n">
-        <v>3.085997405095328</v>
+        <v>3.08599740509533</v>
       </c>
       <c r="D31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.9507764331417912</v>
+        <v>0.9507764331417961</v>
       </c>
       <c r="B32" t="n">
-        <v>0.3295217416659649</v>
+        <v>0.3295217416659637</v>
       </c>
       <c r="C32" t="n">
-        <v>1.601554438276585</v>
+        <v>1.60155443827659</v>
       </c>
       <c r="D32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1.200490831679785</v>
+        <v>1.200490831679786</v>
       </c>
       <c r="B33" t="n">
-        <v>0.273223598926669</v>
+        <v>0.2732235989266686</v>
       </c>
       <c r="C33" t="n">
-        <v>1.871845997115447</v>
+        <v>1.871845997115449</v>
       </c>
       <c r="D33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.2236537360085883</v>
+        <v>0.2236537360085886</v>
       </c>
       <c r="B34" t="n">
-        <v>0.6362699465437972</v>
+        <v>0.636269946543797</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6522891156774182</v>
+        <v>0.6522891156774188</v>
       </c>
       <c r="D34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1.154672888744983</v>
+        <v>1.154672888744984</v>
       </c>
       <c r="B35" t="n">
-        <v>0.2825730825236629</v>
+        <v>0.2825730825236627</v>
       </c>
       <c r="C35" t="n">
-        <v>1.823304051576394</v>
+        <v>1.823304051576395</v>
       </c>
       <c r="D35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1.23543935722114</v>
+        <v>1.235439357221142</v>
       </c>
       <c r="B36" t="n">
-        <v>0.2663518146526981</v>
+        <v>0.2663518146526977</v>
       </c>
       <c r="C36" t="n">
-        <v>1.908594984885502</v>
+        <v>1.908594984885503</v>
       </c>
       <c r="D36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.7306509873324861</v>
+        <v>0.7306509873324792</v>
       </c>
       <c r="B37" t="n">
-        <v>0.3926722595246472</v>
+        <v>0.3926722595246493</v>
       </c>
       <c r="C37" t="n">
-        <v>1.348602413001822</v>
+        <v>1.348602413001814</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -2821,13 +2821,13 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.1638558207844865</v>
+        <v>0.1638558207844868</v>
       </c>
       <c r="B38" t="n">
-        <v>0.6856310839467142</v>
+        <v>0.6856310839467139</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5444955775617802</v>
+        <v>0.5444955775617809</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -2837,13 +2837,13 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.3127434814314999</v>
+        <v>0.3127434814314985</v>
       </c>
       <c r="B39" t="n">
-        <v>0.5760015348351406</v>
+        <v>0.5760015348351415</v>
       </c>
       <c r="C39" t="n">
-        <v>0.7958554389557195</v>
+        <v>0.7958554389557173</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2853,13 +2853,13 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.4413135992851797</v>
+        <v>0.4413135992851749</v>
       </c>
       <c r="B40" t="n">
-        <v>0.5064891174464747</v>
+        <v>0.506489117446477</v>
       </c>
       <c r="C40" t="n">
-        <v>0.9813968236391744</v>
+        <v>0.981396823639168</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
